--- a/data.xlsx
+++ b/data.xlsx
@@ -1,41 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11028"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/awu/Desktop/網頁設計html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\102791\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F188377B-F949-DE45-B4AD-A4D9C6DEE456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="33600" windowHeight="20380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9804"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>化學品</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -169,18 +158,14 @@
   </si>
   <si>
     <t>2024.12.21</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4月</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -329,7 +314,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -342,34 +327,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -666,22 +657,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
-    <col min="5" max="5" width="16.1640625" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="5" max="5" width="16.109375" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" customWidth="1"/>
-    <col min="10" max="10" width="22.1640625" customWidth="1"/>
+    <col min="9" max="9" width="16.21875" customWidth="1"/>
+    <col min="10" max="10" width="22.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -706,14 +697,14 @@
       <c r="H1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -737,20 +728,20 @@
         <v>2026</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="15" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="11">
         <v>400</v>
       </c>
       <c r="C3" s="4">
@@ -763,7 +754,7 @@
         <f t="shared" si="0"/>
         <v>0.15</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="14" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="1">
@@ -775,21 +766,21 @@
       <c r="I3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="32">
+    <row r="4" spans="1:10" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="11">
         <v>1000</v>
       </c>
       <c r="C4" s="4">
         <v>10</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="11">
         <v>3</v>
       </c>
       <c r="E4" s="2">
@@ -808,17 +799,17 @@
       <c r="I4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="15" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12">
         <v>23</v>
       </c>
       <c r="E5" s="2" t="str">
@@ -835,15 +826,15 @@
         <v>2</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="11">
         <v>400</v>
       </c>
       <c r="C6" s="4">
@@ -856,7 +847,7 @@
         <f t="shared" si="0"/>
         <v>1.25</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="1">
@@ -868,21 +859,21 @@
       <c r="I6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="11">
         <v>1000</v>
       </c>
       <c r="C7" s="4">
         <v>500</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="11">
         <v>400</v>
       </c>
       <c r="E7" s="2">
@@ -901,21 +892,21 @@
       <c r="I7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="11">
         <v>400</v>
       </c>
       <c r="C8" s="4">
         <v>75</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="11">
         <v>57</v>
       </c>
       <c r="E8" s="2">
@@ -934,21 +925,21 @@
       <c r="I8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="32">
+    <row r="9" spans="1:10" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="11">
         <v>1000</v>
       </c>
       <c r="C9" s="4">
         <v>10</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="11">
         <v>3</v>
       </c>
       <c r="E9" s="2">
@@ -967,21 +958,21 @@
       <c r="I9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="16">
+    <row r="10" spans="1:10" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="11">
         <v>1000</v>
       </c>
       <c r="C10" s="4">
         <v>10</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="11">
         <v>4</v>
       </c>
       <c r="E10" s="2">
@@ -1000,21 +991,21 @@
       <c r="I10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="32">
+    <row r="11" spans="1:10" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="11">
         <v>2000</v>
       </c>
       <c r="C11" s="4">
         <v>400</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="11">
         <v>100</v>
       </c>
       <c r="E11" s="2">
@@ -1033,21 +1024,21 @@
       <c r="I11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="16">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="11">
         <v>1000</v>
       </c>
       <c r="C12" s="4">
         <v>30</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="11">
         <v>19</v>
       </c>
       <c r="E12" s="2">
@@ -1066,12 +1057,12 @@
       <c r="I12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="15" t="s">
         <v>34</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I12">
+  <sortState ref="A2:I12">
     <sortCondition ref="F2:F12"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
